--- a/barcode/intermediate_result.xlsx
+++ b/barcode/intermediate_result.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="141">
   <si>
     <t>Артикул</t>
   </si>
@@ -28,193 +28,373 @@
     <t>место</t>
   </si>
   <si>
+    <t>Термонаклейка для одежды: набор Черепашки ниндзя turtles TMNT</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Пионы розовый Peonies</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Ловец снов акварель</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Перья Украшение Ожерелье</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: набор Том и Джерри Tom and Jerry</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Белый волк с цветами и узорами</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: набор Щенячий Патруль Paw Patrol</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Синий Акварель</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Аист оранжевый круг</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Орхидея Цветы Розовые</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Морская Ракушка Силует</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Белая Лошадь Цветы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Подсолнухи Цветы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Колибри 2шт</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Магнолия 3шт розовые</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Пионы надпись</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Мэрилин Монро Поп арт жвачка</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Пара леопардов в ночной листве</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Королева с бокалом игральная карта</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кит в золотом дизайне космос</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сердце Букет Цветы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Бабочка зеленная листья</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка Венок Луна Акварель</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Лотос розовый золотистый</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Пионы красные Pionies</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Розовые Spring Blossoms</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Бабочки 4шт небо внутри</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Тюльпаны 5шт белые</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Мак фиолетовый</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Леопард пятна сердечки голова</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кассета цветы Vintage Soul</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Большая волна в Канагаве Солнце</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Фламинго Flamingo цветы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сердце разынй окрас</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Медуза Горгона черно-белый</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сейлор Мун Sailor Moon голубой фон</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Лев Краски Дизайн</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка гладиолус цветы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Зайка балерина</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Человек Паук Лого позади</t>
+  </si>
+  <si>
     <t>Термонаклейка для одежды: Весёлый енот выглядывает</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: набор Черепашки ниндзя turtles TMNT</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: набор Щенячий Патруль Paw Patrol</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Белая Лошадь Цветы</t>
+    <t>Термонаклейка для одежды: Радужный котенок счастливый</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Тигр спит среди тропических цветов</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кошка розово-фиолетовая крупный план</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Тигр с букетом жёлтых тюльпанов</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Маленький принц на синем ките</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девочка и Лиса</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Белый Кот в цветах</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кот цветы внутри</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка Силует Акварель Лес</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Чайка силует море внутри</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Магнолия фиолетовая Garden</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Тюльпаны 3шт розовые</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Магнолия белые Botanical</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Ирисы акварелью Синий</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Формы термозаплатка</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Матрешка цветы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Перья Яркие Wild Spirit</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Синии Амариллис</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Лес Гитара Закат</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Мэрилин Монро фото буквы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Цветы Желтый Мак</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Микки Маус бабочки цветы силуэт</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кит хвост из волн море океан</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сердце Love is Wild</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сердце Большая волна в Канагаве</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Крылья красочные маслом</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка силует туман лес птицы</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка макияж Хэллоуин</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Единороги голубой и розовый</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Радужный котенок счастливый</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Улыбающийся лисенок в снегу</t>
+    <t>Термонаклейка для одежды: Спанч Боб и друзья</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девочка в зелёном с подсолнухом</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девочка с маком в руках</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девочка в розовом платье</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Девочка Ангел с хвостами</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Ёжики в кружках с сердечками</t>
-  </si>
-  <si>
     <t>Термонаклейка для одежды: Лошадь в золотых и мраморных тонах</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Тигр спит среди тропических цветов</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Ловец снов акварель</t>
+    <t>Термонаклейка для одежды: Девушка в цветах и золотом круге</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кит в голубых и розовых оттенках</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Аниме девочка с мыльными пузырями</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Чёрная кошка с узорами на фоне луны</t>
+    <t>Термонаклейка для одежды: Тигр в витражном стиле</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Сова в цветах</t>
   </si>
   <si>
+    <t>Термонаклейка для одежды: Золотой лев в изысканном узоре</t>
+  </si>
+  <si>
     <t>Термонаклейка для одежды: Чёрный волк красный луна</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Кит в золотом дизайне космос</t>
-  </si>
-  <si>
     <t>Термонаклейка для одежды: Лошадь в космических красках</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Девушка-кошка с чёрным котом поцелуй</t>
   </si>
   <si>
+    <t>Термонаклейка для одежды: Аниме девочка в цветах и фонарях</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: набор Соник Sonic</t>
+  </si>
+  <si>
     <t>Термонаклейка для одежды: набор Винни Пух</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: набор Том и Джерри Tom and Jerry</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Девочка и Лиса</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Орхидея Цветы Розовые</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Девушка Венок Луна Акварель</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Подсолнухи Цветы</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Девушка Аниме Япония Красное Солнце</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Цветы Пионы красные Pionies</t>
+    <t>Термонаклейка для одежды: Кит в Цветах</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Черепаха Цветы на панцире</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка Силует Закат</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Пантера силует внутри цветы</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Девушка с колибри роза кольцо</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Цветы Тюльпаны 5шт белые</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Цветы Магнолия 3шт розовые</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Цветы Мак фиолетовый</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Формы термозаплатка</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Звезды Черные термозаплатка</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Звезды Белые термозаплатка</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Перья Украшение Ожерелье</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Леопард пятна сердечки голова</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Большая волна в Канагаве Солнце</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Минни Маус и бабочка</t>
+    <t>Термонаклейка для одежды: Матрешка с хлебом</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сердце Бабочки летят</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Дисней утка Дейзи и Минни пис</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Секс в большом городе подруги</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Лес Гитара Закат</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Мэрилин Монро буквы</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Микки Маус бабочки цветы силуэт</t>
+    <t>Термонаклейка для одежды: Мопс Собачка попа секси</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Котенок розовый закат звезды</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Сердце Love is Wild</t>
-  </si>
-  <si>
     <t>Термонаклейка для одежды: Подсолнух Ван Гог</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Цветы Пионы надпись</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Сердце разынй окрас</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Черный Кот Звезды Астрология</t>
+    <t>Термонаклейка для одежды: Девушка бабочка Ван Гог</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка на закате держат руки море</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Одри Хепбёрн холст Vogue</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Девушка силует обнимают природа</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Спанч Боб и друзья</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Марвел супергерои 4 верт фона</t>
+    <t>Термонаклейка для одежды: Леопардовое сердце розовое</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сейлор Мун Sailor Moon радуется</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Лило и Стич сидят</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Человек Паук Лого круг</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Единорог с ромашкой сердечки</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Зайка балерина</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Человек Паук Лого позади</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Котята на качелях</t>
+    <t>Термонаклейка для одежды: Зайчик ромашка в руках</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Чёрный кот Catzilla Годзилла луч</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Череп в куртке Punk Not Dead</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Кибер-девушка в стиле аниме</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Акира Глаз ядерный взрыв</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Медведь, волк и матрёшка</t>
+    <t>Термонаклейка для одежды: Лев в жёлтой куртке</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Череп с рогами и логотипом Metallica</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Кибердевушка с капюшоном</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Белый волк с красным солнцем</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Самурай в маске воина</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Вид на пляж из домика</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка в синем у моря</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Сияй, чёрт возьми - корона</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Чайка и морской пейзаж</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Чёрная кошка с кругом цифра 9</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Лимоны и морской пейзаж</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Роза с бутоном акварель</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Фламинго трое на воде право</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Гортензии акварель</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Прикосновение рук Сотворения Адама</t>
   </si>
   <si>
     <t>Термонаклейка для одежды: Графичное лицо в чёрно-белом</t>
@@ -223,25 +403,37 @@
     <t>Термонаклейка для одежды: Не буди лихо пока тихо</t>
   </si>
   <si>
+    <t>Термонаклейка для одежды: Девушка ebis ono by horse</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девочка и кот у моря</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Тюльпаны акварель</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Девушка в золотых трещинах</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Рука жест рок металл</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Балерина в белом платье</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Воздушный шар из пионов</t>
+  </si>
+  <si>
     <t>Термонаклейка для одежды: Треснувшая античная скульптура</t>
   </si>
   <si>
-    <t>Термонаклейка для одежды: Девушка в золотых трещинах</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Прикосновение рук Сотворения Адама</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Чёрная кошка с кругом цифра 9</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Чёрная кошка и луна</t>
-  </si>
-  <si>
-    <t>Термонаклейка для одежды: Гарри Поттер и Хагрид курят</t>
-  </si>
-  <si>
     <t>Термонаклейка для одежды: Египетская кошка в золоте</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Итальянская набережная</t>
+  </si>
+  <si>
+    <t>Термонаклейка для одежды: Медуза в очках и с змеями</t>
   </si>
   <si>
     <t>Нет</t>
@@ -602,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -624,10 +816,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C2">
-        <v>3824405590</v>
+        <v>12255224135</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -635,10 +827,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C3">
-        <v>3501492610</v>
+        <v>11378017847</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -646,10 +838,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C4">
-        <v>3501482146</v>
+        <v>11098668138</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -657,10 +849,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C5">
-        <v>3477303742</v>
+        <v>10730581687</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -668,10 +860,10 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C6">
-        <v>3012638794</v>
+        <v>10504473396</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -679,10 +871,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C7">
-        <v>1912202740</v>
+        <v>9248888280</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -690,10 +882,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C8">
-        <v>1912202105</v>
+        <v>8753705365</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -701,10 +893,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C9">
-        <v>1912202033</v>
+        <v>8693258420</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -712,10 +904,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C10">
-        <v>1912201742</v>
+        <v>8125231925</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -723,10 +915,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C11">
-        <v>1849778151</v>
+        <v>6954610980</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -734,10 +926,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C12">
-        <v>1849778044</v>
+        <v>6954610140</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -745,10 +937,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C13">
-        <v>1849778023</v>
+        <v>6954607484</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -756,10 +948,10 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C14">
-        <v>1849777862</v>
+        <v>6954606452</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -767,10 +959,10 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C15">
-        <v>1849777815</v>
+        <v>6500185104</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -778,10 +970,10 @@
         <v>18</v>
       </c>
       <c r="B16" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C16">
-        <v>1849777716</v>
+        <v>6500184988</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -789,10 +981,10 @@
         <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C17">
-        <v>1849777650</v>
+        <v>6088078272</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -800,10 +992,10 @@
         <v>20</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C18">
-        <v>1849777647</v>
+        <v>6025280020</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -811,10 +1003,10 @@
         <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C19">
-        <v>1849777600</v>
+        <v>5549333718</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -822,10 +1014,10 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C20">
-        <v>1849777586</v>
+        <v>5549333499</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -833,10 +1025,10 @@
         <v>23</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C21">
-        <v>1750745576</v>
+        <v>5549332941</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -844,10 +1036,10 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C22">
-        <v>1750745566</v>
+        <v>5215957470</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -855,10 +1047,10 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C23">
-        <v>1738653148</v>
+        <v>5215957197</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -866,10 +1058,10 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C24">
-        <v>1738652745</v>
+        <v>5215956441</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -877,10 +1069,10 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C25">
-        <v>1738652147</v>
+        <v>5215955763</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -888,10 +1080,10 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C26">
-        <v>1738651613</v>
+        <v>4880516634</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -899,10 +1091,10 @@
         <v>29</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C27">
-        <v>1738651525</v>
+        <v>4880516301</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -910,10 +1102,10 @@
         <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C28">
-        <v>1626838878</v>
+        <v>4880516136</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -921,10 +1113,10 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C29">
-        <v>1626838871</v>
+        <v>4876293549</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -932,10 +1124,10 @@
         <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C30">
-        <v>1625431183</v>
+        <v>4875138681</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -943,10 +1135,10 @@
         <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C31">
-        <v>1625046247</v>
+        <v>4598819043</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -954,10 +1146,10 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C32">
-        <v>1625046227</v>
+        <v>4598817948</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -965,10 +1157,10 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C33">
-        <v>1563383294</v>
+        <v>4598816850</v>
       </c>
     </row>
     <row r="34" spans="1:3">
@@ -976,10 +1168,10 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C34">
-        <v>1563383242</v>
+        <v>4598815794</v>
       </c>
     </row>
     <row r="35" spans="1:3">
@@ -987,10 +1179,10 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C35">
-        <v>1563382131</v>
+        <v>4566058494</v>
       </c>
     </row>
     <row r="36" spans="1:3">
@@ -998,10 +1190,10 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C36">
-        <v>1532940241</v>
+        <v>4566058422</v>
       </c>
     </row>
     <row r="37" spans="1:3">
@@ -1009,10 +1201,10 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C37">
-        <v>1532939681</v>
+        <v>4518994404</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -1020,10 +1212,10 @@
         <v>40</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C38">
-        <v>1532938950</v>
+        <v>4518993498</v>
       </c>
     </row>
     <row r="39" spans="1:3">
@@ -1031,10 +1223,10 @@
         <v>41</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C39">
-        <v>1532938464</v>
+        <v>4518959460</v>
       </c>
     </row>
     <row r="40" spans="1:3">
@@ -1042,10 +1234,10 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C40">
-        <v>1522067175</v>
+        <v>4518956556</v>
       </c>
     </row>
     <row r="41" spans="1:3">
@@ -1053,10 +1245,10 @@
         <v>43</v>
       </c>
       <c r="B41" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C41">
-        <v>1522021193</v>
+        <v>4518955344</v>
       </c>
     </row>
     <row r="42" spans="1:3">
@@ -1064,10 +1256,10 @@
         <v>44</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C42">
-        <v>1522021181</v>
+        <v>3824405590</v>
       </c>
     </row>
     <row r="43" spans="1:3">
@@ -1075,10 +1267,10 @@
         <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C43">
-        <v>1522020596</v>
+        <v>3824405480</v>
       </c>
     </row>
     <row r="44" spans="1:3">
@@ -1086,10 +1278,10 @@
         <v>46</v>
       </c>
       <c r="B44" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C44">
-        <v>1522019743</v>
+        <v>3699556088</v>
       </c>
     </row>
     <row r="45" spans="1:3">
@@ -1097,10 +1289,10 @@
         <v>47</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C45">
-        <v>1522019725</v>
+        <v>3699556080</v>
       </c>
     </row>
     <row r="46" spans="1:3">
@@ -1108,10 +1300,10 @@
         <v>48</v>
       </c>
       <c r="B46" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C46">
-        <v>1522019636</v>
+        <v>3699555786</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -1119,10 +1311,10 @@
         <v>49</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C47">
-        <v>1522019568</v>
+        <v>3699555582</v>
       </c>
     </row>
     <row r="48" spans="1:3">
@@ -1130,10 +1322,10 @@
         <v>50</v>
       </c>
       <c r="B48" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C48">
-        <v>1522019498</v>
+        <v>3477306296</v>
       </c>
     </row>
     <row r="49" spans="1:3">
@@ -1141,10 +1333,10 @@
         <v>51</v>
       </c>
       <c r="B49" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C49">
-        <v>1522019292</v>
+        <v>3477305932</v>
       </c>
     </row>
     <row r="50" spans="1:3">
@@ -1152,10 +1344,10 @@
         <v>52</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C50">
-        <v>1506332421</v>
+        <v>3477305638</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -1163,10 +1355,10 @@
         <v>53</v>
       </c>
       <c r="B51" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C51">
-        <v>1506331474</v>
+        <v>3477304734</v>
       </c>
     </row>
     <row r="52" spans="1:3">
@@ -1174,10 +1366,10 @@
         <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C52">
-        <v>1506319347</v>
+        <v>3253677910</v>
       </c>
     </row>
     <row r="53" spans="1:3">
@@ -1185,10 +1377,10 @@
         <v>55</v>
       </c>
       <c r="B53" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C53">
-        <v>1506319337</v>
+        <v>3253676978</v>
       </c>
     </row>
     <row r="54" spans="1:3">
@@ -1196,10 +1388,10 @@
         <v>56</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C54">
-        <v>1506319334</v>
+        <v>3250862096</v>
       </c>
     </row>
     <row r="55" spans="1:3">
@@ -1207,10 +1399,10 @@
         <v>57</v>
       </c>
       <c r="B55" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C55">
-        <v>1506319072</v>
+        <v>3250092668</v>
       </c>
     </row>
     <row r="56" spans="1:3">
@@ -1218,10 +1410,10 @@
         <v>58</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C56">
-        <v>1506319032</v>
+        <v>3250092618</v>
       </c>
     </row>
     <row r="57" spans="1:3">
@@ -1229,10 +1421,10 @@
         <v>59</v>
       </c>
       <c r="B57" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C57">
-        <v>1506318852</v>
+        <v>3126766588</v>
       </c>
     </row>
     <row r="58" spans="1:3">
@@ -1240,10 +1432,10 @@
         <v>60</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C58">
-        <v>1506318448</v>
+        <v>3065876408</v>
       </c>
     </row>
     <row r="59" spans="1:3">
@@ -1251,10 +1443,10 @@
         <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C59">
-        <v>1506318429</v>
+        <v>3065876372</v>
       </c>
     </row>
     <row r="60" spans="1:3">
@@ -1262,10 +1454,10 @@
         <v>62</v>
       </c>
       <c r="B60" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C60">
-        <v>-1820536169</v>
+        <v>3065875890</v>
       </c>
     </row>
     <row r="61" spans="1:3">
@@ -1273,10 +1465,10 @@
         <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C61">
-        <v>-1820713041</v>
+        <v>3044042386</v>
       </c>
     </row>
     <row r="62" spans="1:3">
@@ -1284,10 +1476,10 @@
         <v>64</v>
       </c>
       <c r="B62" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C62">
-        <v>-1820713208</v>
+        <v>3044042006</v>
       </c>
     </row>
     <row r="63" spans="1:3">
@@ -1295,10 +1487,10 @@
         <v>65</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C63">
-        <v>-1820715615</v>
+        <v>3044041438</v>
       </c>
     </row>
     <row r="64" spans="1:3">
@@ -1306,10 +1498,10 @@
         <v>66</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C64">
-        <v>-1844988487</v>
+        <v>3044041192</v>
       </c>
     </row>
     <row r="65" spans="1:3">
@@ -1317,10 +1509,10 @@
         <v>67</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C65">
-        <v>-1844988622</v>
+        <v>3044039466</v>
       </c>
     </row>
     <row r="66" spans="1:3">
@@ -1328,10 +1520,10 @@
         <v>68</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C66">
-        <v>-1844988763</v>
+        <v>3044039450</v>
       </c>
     </row>
     <row r="67" spans="1:3">
@@ -1339,10 +1531,10 @@
         <v>69</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C67">
-        <v>-1844989181</v>
+        <v>3044039294</v>
       </c>
     </row>
     <row r="68" spans="1:3">
@@ -1350,10 +1542,10 @@
         <v>70</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C68">
-        <v>-1844989673</v>
+        <v>3044039128</v>
       </c>
     </row>
     <row r="69" spans="1:3">
@@ -1361,10 +1553,10 @@
         <v>71</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C69">
-        <v>-1844989807</v>
+        <v>3044038748</v>
       </c>
     </row>
     <row r="70" spans="1:3">
@@ -1372,10 +1564,10 @@
         <v>72</v>
       </c>
       <c r="B70" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C70">
-        <v>-1844990206</v>
+        <v>3012663330</v>
       </c>
     </row>
     <row r="71" spans="1:3">
@@ -1383,10 +1575,10 @@
         <v>73</v>
       </c>
       <c r="B71" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C71">
-        <v>-1844990310</v>
+        <v>3012638794</v>
       </c>
     </row>
     <row r="72" spans="1:3">
@@ -1394,10 +1586,10 @@
         <v>74</v>
       </c>
       <c r="B72" t="s">
-        <v>76</v>
+        <v>140</v>
       </c>
       <c r="C72">
-        <v>-3641430742</v>
+        <v>3012638694</v>
       </c>
     </row>
     <row r="73" spans="1:3">
@@ -1405,10 +1597,714 @@
         <v>75</v>
       </c>
       <c r="B73" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73">
+        <v>1912202762</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>76</v>
       </c>
-      <c r="C73">
-        <v>-3689979584</v>
+      <c r="B74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74">
+        <v>1912202150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75">
+        <v>1912202099</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" t="s">
+        <v>140</v>
+      </c>
+      <c r="C76">
+        <v>1912202033</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77">
+        <v>1849778151</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" t="s">
+        <v>140</v>
+      </c>
+      <c r="C78">
+        <v>1849778110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>81</v>
+      </c>
+      <c r="B79" t="s">
+        <v>140</v>
+      </c>
+      <c r="C79">
+        <v>1849777981</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>82</v>
+      </c>
+      <c r="B80" t="s">
+        <v>140</v>
+      </c>
+      <c r="C80">
+        <v>1849777862</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>83</v>
+      </c>
+      <c r="B81" t="s">
+        <v>140</v>
+      </c>
+      <c r="C81">
+        <v>1849777720</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3">
+      <c r="A82" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82" t="s">
+        <v>140</v>
+      </c>
+      <c r="C82">
+        <v>1849777716</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3">
+      <c r="A83" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83" t="s">
+        <v>140</v>
+      </c>
+      <c r="C83">
+        <v>1849777651</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3">
+      <c r="A84" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84">
+        <v>1849777650</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3">
+      <c r="A85" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85" t="s">
+        <v>140</v>
+      </c>
+      <c r="C85">
+        <v>1849777600</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3">
+      <c r="A86" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86" t="s">
+        <v>140</v>
+      </c>
+      <c r="C86">
+        <v>1849777586</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3">
+      <c r="A87" t="s">
+        <v>89</v>
+      </c>
+      <c r="B87" t="s">
+        <v>140</v>
+      </c>
+      <c r="C87">
+        <v>1849771468</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3">
+      <c r="A88" t="s">
+        <v>90</v>
+      </c>
+      <c r="B88" t="s">
+        <v>140</v>
+      </c>
+      <c r="C88">
+        <v>1750746301</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3">
+      <c r="A89" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" t="s">
+        <v>140</v>
+      </c>
+      <c r="C89">
+        <v>1750745576</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3">
+      <c r="A90" t="s">
+        <v>92</v>
+      </c>
+      <c r="B90" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90">
+        <v>1738652878</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3">
+      <c r="A91" t="s">
+        <v>93</v>
+      </c>
+      <c r="B91" t="s">
+        <v>140</v>
+      </c>
+      <c r="C91">
+        <v>1738652063</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3">
+      <c r="A92" t="s">
+        <v>94</v>
+      </c>
+      <c r="B92" t="s">
+        <v>140</v>
+      </c>
+      <c r="C92">
+        <v>1738651975</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3">
+      <c r="A93" t="s">
+        <v>95</v>
+      </c>
+      <c r="B93" t="s">
+        <v>140</v>
+      </c>
+      <c r="C93">
+        <v>1626838959</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3">
+      <c r="A94" t="s">
+        <v>96</v>
+      </c>
+      <c r="B94" t="s">
+        <v>140</v>
+      </c>
+      <c r="C94">
+        <v>1626838871</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3">
+      <c r="A95" t="s">
+        <v>97</v>
+      </c>
+      <c r="B95" t="s">
+        <v>140</v>
+      </c>
+      <c r="C95">
+        <v>1626838716</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3">
+      <c r="A96" t="s">
+        <v>98</v>
+      </c>
+      <c r="B96" t="s">
+        <v>140</v>
+      </c>
+      <c r="C96">
+        <v>1532938508</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" t="s">
+        <v>99</v>
+      </c>
+      <c r="B97" t="s">
+        <v>140</v>
+      </c>
+      <c r="C97">
+        <v>1532937844</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3">
+      <c r="A98" t="s">
+        <v>100</v>
+      </c>
+      <c r="B98" t="s">
+        <v>140</v>
+      </c>
+      <c r="C98">
+        <v>1522067175</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
+      <c r="A99" t="s">
+        <v>101</v>
+      </c>
+      <c r="B99" t="s">
+        <v>140</v>
+      </c>
+      <c r="C99">
+        <v>1522020897</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
+      <c r="A100" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" t="s">
+        <v>140</v>
+      </c>
+      <c r="C100">
+        <v>1522019743</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" t="s">
+        <v>103</v>
+      </c>
+      <c r="B101" t="s">
+        <v>140</v>
+      </c>
+      <c r="C101">
+        <v>1522019636</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" t="s">
+        <v>104</v>
+      </c>
+      <c r="B102" t="s">
+        <v>140</v>
+      </c>
+      <c r="C102">
+        <v>1522019613</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" t="s">
+        <v>105</v>
+      </c>
+      <c r="B103" t="s">
+        <v>140</v>
+      </c>
+      <c r="C103">
+        <v>1506332556</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" t="s">
+        <v>106</v>
+      </c>
+      <c r="B104" t="s">
+        <v>140</v>
+      </c>
+      <c r="C104">
+        <v>1506332421</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" t="s">
+        <v>140</v>
+      </c>
+      <c r="C105">
+        <v>1506320308</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" t="s">
+        <v>108</v>
+      </c>
+      <c r="B106" t="s">
+        <v>140</v>
+      </c>
+      <c r="C106">
+        <v>1506320185</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" t="s">
+        <v>109</v>
+      </c>
+      <c r="B107" t="s">
+        <v>140</v>
+      </c>
+      <c r="C107">
+        <v>1506319334</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" t="s">
+        <v>110</v>
+      </c>
+      <c r="B108" t="s">
+        <v>140</v>
+      </c>
+      <c r="C108">
+        <v>1506318053</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" t="s">
+        <v>111</v>
+      </c>
+      <c r="B109" t="s">
+        <v>140</v>
+      </c>
+      <c r="C109">
+        <v>-1820536169</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3">
+      <c r="A110" t="s">
+        <v>112</v>
+      </c>
+      <c r="B110" t="s">
+        <v>140</v>
+      </c>
+      <c r="C110">
+        <v>-1820711704</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3">
+      <c r="A111" t="s">
+        <v>113</v>
+      </c>
+      <c r="B111" t="s">
+        <v>140</v>
+      </c>
+      <c r="C111">
+        <v>-1820712060</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3">
+      <c r="A112" t="s">
+        <v>114</v>
+      </c>
+      <c r="B112" t="s">
+        <v>140</v>
+      </c>
+      <c r="C112">
+        <v>-1820712657</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3">
+      <c r="A113" t="s">
+        <v>115</v>
+      </c>
+      <c r="B113" t="s">
+        <v>140</v>
+      </c>
+      <c r="C113">
+        <v>-1820713414</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3">
+      <c r="A114" t="s">
+        <v>116</v>
+      </c>
+      <c r="B114" t="s">
+        <v>140</v>
+      </c>
+      <c r="C114">
+        <v>-1820715725</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3">
+      <c r="A115" t="s">
+        <v>117</v>
+      </c>
+      <c r="B115" t="s">
+        <v>140</v>
+      </c>
+      <c r="C115">
+        <v>-1844985563</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3">
+      <c r="A116" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" t="s">
+        <v>140</v>
+      </c>
+      <c r="C116">
+        <v>-1844989458</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3">
+      <c r="A117" t="s">
+        <v>119</v>
+      </c>
+      <c r="B117" t="s">
+        <v>140</v>
+      </c>
+      <c r="C117">
+        <v>-1844989466</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3">
+      <c r="A118" t="s">
+        <v>120</v>
+      </c>
+      <c r="B118" t="s">
+        <v>140</v>
+      </c>
+      <c r="C118">
+        <v>-1844990165</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3">
+      <c r="A119" t="s">
+        <v>121</v>
+      </c>
+      <c r="B119" t="s">
+        <v>140</v>
+      </c>
+      <c r="C119">
+        <v>-1844990206</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3">
+      <c r="A120" t="s">
+        <v>122</v>
+      </c>
+      <c r="B120" t="s">
+        <v>140</v>
+      </c>
+      <c r="C120">
+        <v>-1844990277</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3">
+      <c r="A121" t="s">
+        <v>123</v>
+      </c>
+      <c r="B121" t="s">
+        <v>140</v>
+      </c>
+      <c r="C121">
+        <v>-3689975300</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3">
+      <c r="A122" t="s">
+        <v>124</v>
+      </c>
+      <c r="B122" t="s">
+        <v>140</v>
+      </c>
+      <c r="C122">
+        <v>-3689975402</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3">
+      <c r="A123" t="s">
+        <v>125</v>
+      </c>
+      <c r="B123" t="s">
+        <v>140</v>
+      </c>
+      <c r="C123">
+        <v>-3689978896</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3">
+      <c r="A124" t="s">
+        <v>126</v>
+      </c>
+      <c r="B124" t="s">
+        <v>140</v>
+      </c>
+      <c r="C124">
+        <v>-3689979614</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3">
+      <c r="A125" t="s">
+        <v>127</v>
+      </c>
+      <c r="B125" t="s">
+        <v>140</v>
+      </c>
+      <c r="C125">
+        <v>-5534965866</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3">
+      <c r="A126" t="s">
+        <v>128</v>
+      </c>
+      <c r="B126" t="s">
+        <v>140</v>
+      </c>
+      <c r="C126">
+        <v>-5534966289</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3">
+      <c r="A127" t="s">
+        <v>129</v>
+      </c>
+      <c r="B127" t="s">
+        <v>140</v>
+      </c>
+      <c r="C127">
+        <v>-5534967033</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3">
+      <c r="A128" t="s">
+        <v>130</v>
+      </c>
+      <c r="B128" t="s">
+        <v>140</v>
+      </c>
+      <c r="C128">
+        <v>-5534967600</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3">
+      <c r="A129" t="s">
+        <v>131</v>
+      </c>
+      <c r="B129" t="s">
+        <v>140</v>
+      </c>
+      <c r="C129">
+        <v>-5534968452</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3">
+      <c r="A130" t="s">
+        <v>132</v>
+      </c>
+      <c r="B130" t="s">
+        <v>140</v>
+      </c>
+      <c r="C130">
+        <v>-5534969019</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3">
+      <c r="A131" t="s">
+        <v>133</v>
+      </c>
+      <c r="B131" t="s">
+        <v>140</v>
+      </c>
+      <c r="C131">
+        <v>-5534970525</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3">
+      <c r="A132" t="s">
+        <v>134</v>
+      </c>
+      <c r="B132" t="s">
+        <v>140</v>
+      </c>
+      <c r="C132">
+        <v>-7379960580</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3">
+      <c r="A133" t="s">
+        <v>135</v>
+      </c>
+      <c r="B133" t="s">
+        <v>140</v>
+      </c>
+      <c r="C133">
+        <v>-9224943700</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3">
+      <c r="A134" t="s">
+        <v>136</v>
+      </c>
+      <c r="B134" t="s">
+        <v>140</v>
+      </c>
+      <c r="C134">
+        <v>-9224945905</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3">
+      <c r="A135" t="s">
+        <v>137</v>
+      </c>
+      <c r="B135" t="s">
+        <v>140</v>
+      </c>
+      <c r="C135">
+        <v>-9224948960</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3">
+      <c r="A136" t="s">
+        <v>138</v>
+      </c>
+      <c r="B136" t="s">
+        <v>140</v>
+      </c>
+      <c r="C136">
+        <v>-9224952680</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3">
+      <c r="A137" t="s">
+        <v>139</v>
+      </c>
+      <c r="B137" t="s">
+        <v>140</v>
+      </c>
+      <c r="C137">
+        <v>-11069941578</v>
       </c>
     </row>
   </sheetData>
